--- a/data_extactor/batch_10_fa/batch_0087_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0087_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | چالاکی دست | حساسیت به مسئله | تجسم فضایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | چالاکی انگشتان | توجه انتخابی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری گسترده | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | مهارت انگشتان | توجه انتخابی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | داخل ساختمان، با تهویه مطبوع | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و قطعه‌قطعه کردن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار حفاری و سوراخ‌کاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | یادگیری فعال | گوش دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تجسم فضایی | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | چالاکی انگشتان | چالاکی دست | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | ثبات دست و بازو | هماهنگی چند عضو | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | استدلال استقرایی | درک کتبی</t>
+          <t>تجسم | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | مهارت انگشتان | مهارت دستی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | ثبات دست و بازو | هماهنگی چند عضو | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | ارتباط با دیگران | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه یا تیم کاری | فراوانی تصمیم‌گیری | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | ارتباط با دیگران | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستگاه‌های برش و قطعه‌قطعه کردن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار حفاری و سوراخ‌کاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | مدل‌سازان، فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | الگوپردازان، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد، فلز و پلاستیک | سازندگان و مونتاژکنندگان سازه‌های فلزی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | الگوسازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EZ Pipe | Fred's Tip Cartridge Picker | IBM Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | OmniFleet Equipment Maintenance Management | Oracle Database | نرم‌افزار بایگانی اسناد | Scientific Software Group Filter Drain FD | Value Analysis</t>
+          <t>EZ Pipe | Fred's Tip Cartridge Picker | IBM Notes | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | OmniFleet Equipment Maintenance Management | Oracle Database | نرم‌افزار ثبت سوابق | Scientific Software Group Filter Drain FD | Value Analysis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | چالاکی انگشتان | دقت کنترل | چالاکی دست | استدلال قیاسی | درک شفاهی | توجه انتخابی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت انگشتان | دقت کنترل | مهارت دستی | استدلال قیاسی | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | داخل ساختمان، بدون تهویه مطبوع | صرف زمان به صورت ایستاده</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و قطعه‌قطعه کردن | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکنندگان سازه‌های فلزی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Email software | Linux | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SAP software | Tool center point TCP setting software</t>
+          <t>نرم‌افزار ایمیل | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار SAP | Tool center point TCP setting software</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | مانیتورینگ</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | امور اداری و مدیریت | طراحی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | تجسم فضایی | ثبات دست و بازو | چالاکی دست | هماهنگی چند عضو | توجه انتخابی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | بینایی دور | انعطاف‌پذیری گسترده | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | چالاکی انگشتان | وضوح گفتار</t>
+          <t>بینایی نزدیک | دقت کنترل | تجسم | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | توجه انتخابی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | وضوح گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان به صورت ایستاده | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | هماهنگ‌سازی یا هدایت دیگران در انجام فعالیت‌های کاری | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | فشار زمانی | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دستگاه‌های برش و قطعه‌قطعه کردن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش, پانچ و پرس، فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکنندگان سازه‌های فلزی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | چالاکی دست | حساسیت به مسئله | قدرت تنه | قدرت ایستا | دقت کنترل | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | چالاکی انگشتان | استقامت | وضوح گفتار | تشخیص گفتار | کنترل نرخ | تجسم فضایی | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری گسترده | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی | درک کتبی | درک شفاهی | توجه شنیداری | درک عمق</t>
+          <t>ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | قدرت تنه | قدرت ایستا | دقت کنترل | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | مهارت انگشتان | استقامت | وضوح گفتار | تشخیص گفتار | کنترل نرخ | تجسم | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی | درک کتبی | درک شفاهی | توجه شنیداری | درک عمق</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف مشابه | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، بدون تهویه مطبوع | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | دستگاه‌های برش و قطعه‌قطعه کردن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | اپراتورها و متصدیان کوره، کوره پخت، آون، خشک‌کن و دیگ ذوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجر نسوز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان دستگاه‌های سفیدگری و رنگرزی منسوجات | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ریاضیات | مانیتورینگ | تفکر انتقادی | درک مطلب</t>
+          <t>ریاضیات | نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ریاضیات | طراحی | مکانیک | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری | ساختمان و ساخت‌وساز | امور اداری و مدیریت | کامپیوتر و الکترونیک | آموزش و تربیت</t>
+          <t>ریاضیات | طراحی | مکانیک | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری | ساختمان و ساخت‌وساز | مدیریت و اداره | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | تجسم فضایی | حساسیت به مسئله | چالاکی دست | ترتیب‌دهی اطلاعات | استدلال قیاسی | چالاکی انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | درک کتبی | درک شفاهی | قدرت تنه | هماهنگی چند عضو | دقت کنترل | توانایی کار با اعداد | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | توجه شنیداری | بینایی دور</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | تجسم | حساسیت به مسئله | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | درک کتبی | درک شفاهی | قدرت تنه | هماهنگی چند عضو | دقت کنترل | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | توجه شنیداری | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، بدون تهویه مطبوع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | ارتباط با دیگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا نامناسب | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | ارتباط با دیگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | کابینت‌سازان و نجاران کارگاهی | نجاران | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | ماشین‌کاران | نقشه کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | مدل‌سازان، فلز و پلاستیک | مدل‌سازان، چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوپردازان، فلز و پلاستیک | الگوپردازان، چوب | ورق‌کاران فلزی | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکنندگان سازه‌های فلزی | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | کابینت‌سازان و نجاران نیمکت | نجّاران | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | ماشین‌کاران | نقشه‌کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | مانیتورینگ | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | شیمی | زبان انگلیسی | مکانیک | مهندسی و فناوری | آموزش و تربیت | قانون و حکومت | خدمات مشتری و شخصی | طراحی | امنیت عمومی و امنیت | حمل‌ونقل</t>
+          <t>تولید و فرآوری | ریاضیات | شیمی | زبان انگلیسی | مکانیک | مهندسی و فناوری | آموزش و پرورش | قانون و دولت | خدمات مشتری و شخصی | طراحی | ایمنی و امنیت عمومی | حمل و نقل</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | چالاکی دست | وضوح گفتار | هماهنگی چند عضو | بیان شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | قدرت تنه | قدرت ایستا | چالاکی انگشتان</t>
+          <t>بینایی نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | وضوح گفتار | هماهنگی چند عضو | بیان شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | قدرت تنه | قدرت ایستا | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه یا تیم کاری | داخل ساختمان، بدون تهویه مطبوع | پیامدهای کاری و نتایج سایر کارگران | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارگران | صرف زمان برای راه رفتن یا دویدن | هماهنگ‌سازی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارکنان | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | ریزندگان و ریخته‌گران فلز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان دستگاه‌های سفیدگری و رنگرزی منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | متصدیان و اپراتورهای تجهیزات شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | کارگران نقاشی، پوشش‌دهی و تزیین | ریزندگان و ریخته‌گران فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ</t>
+          <t>تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دست | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | تجسم فضایی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | زمان عکس‌العمل | کنترل نرخ | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | قدرت ایستا | هماهنگی چند عضو</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | زمان عکس‌العمل | کنترل نرخ | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | قدرت ایستا | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | هماهنگ‌سازی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردکن، سنگ‌زنی و صیقل‌دهی | دستگاه‌های برش و قطعه‌قطعه کردن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار حفاری و سوراخ‌کاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری، فلز و پلاستیک | کارگران پرداخت‌کاری و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراشکاری، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان, اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اره‌کشی، چوب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>داخل ساختمان، بدون تهویه مطبوع | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا پیچاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارگران | پیامد خطا | درجه اتوماسیون | اهمیت تکرار وظایف مشابه | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ماشین‌کاران | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | سازندگان ابزار و قالب | کارگران شابلون‌زنی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار سنگ‌زنی، لپینگ، پرداخت‌کاری و صیقل‌دهی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش، فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | ریزندگان و ریخته‌گران فلز | اپراتورها و متصدیان کوره‌های تصفیه فلز | مدل‌سازان، فلز و پلاستیک | اپراتورهای ابزار کنترل عددی کامپیوتری | بازرسان، تست‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | سازندگان و مونتاژکنندگان سازه‌های فلزی | سرپرستان خط اول کارگران تولید و عملیاتی | کارگران تولید، سایر</t>
+          <t>ماشین‌کاران | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | سازندگان ابزار و قالب | کارگران شابلون‌زنی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | ریزندگان و ریخته‌گران فلز | اپراتورها و متصدیان کوره تصفیه فلز | مدل‌سازان فلز و پلاستیک | اپراتورهای ابزار کنترل عددی کامپیوتری | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | سازندگان و مونتاژکاران فلزات سازه‌ای | سرپرستان رده اول کارگران تولید و بهره‌برداری | کارگران تولید، سایر موارد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | تجسم فضایی | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال قیاسی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | تجسم | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | داخل ساختمان، با تهویه مطبوع | ایمیل | مکالمات تلفنی | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف مشابه | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | فناوران و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | ناشران رومیزی | مونتاژکنندگان تجهیزات الکترومکانیکی | حکاکان و قلم‌زنان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان دستگاه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | کارگران رنگ‌آمیزی، پوشش‌دهی و تزئین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | الگوپردازان، فلز و پلاستیک | کارگران فرآیندهای عکاسی و اپراتورهای دستگاه‌های فرآوری | کارگران صحافی و پرداخت‌کاری چاپ | اپراتورهای ماشین چاپ | هنرمندان جلوه‌های ویژه و انیماتورها</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | ناشران رومیزی | مونتاژکاران تجهیزات الکترومکانیکی | حکاکان و تیزاب‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز رایانه | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | کارکنان صحافی و پرداخت چاپ | اپراتورهای ماشین چاپ | هنرمندان جلوه‌های ویژه و انیماتورها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0087_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0087_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | دید نزدیک | چابکی دستی | حساسیت به مسئله | تجسم فضایی | مرتب‌سازی اطلاعات | تشخیص گفتار | دید دور | زمان واکنش | هماهنگی اندام‌ها | چابکی انگشتان | توجه انتخابی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری بدنی | کنترل سرعت | سرعت ادراک | انعطاف‌پذیری بستار | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | تجسم | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | مهارت انگشتان | توجه انتخابی | درک کتبی | درک شفاهی | وضوح گفتار | توجه شنیداری | حساسیت شنوایی | انعطاف‌پذیری دامنه حرکت | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌ابزار کنترل عددی رایانه‌ای CNC | تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | تعمیرکاران ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کاران و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های برش پارچه و پوشاک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | حساسیت به مسئله | دقت کنترل | چابکی انگشتان | چابکی دستی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | ثبات دست و بازو | هماهنگی اندام‌ها | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | استدلال استقرایی | درک کتبی</t>
+          <t>تجسم | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | مهارت انگشتان | مهارت دستی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | ثبات دست و بازو | هماهنگی چند عضو | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | ماشین‌کاران و تراشکاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان صنعتی فلز و پلاستیک | قالب‌ریزان و شکل‌دهندگان غیر از فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگو سازان قطعات فلزی و پلاستیکی | تنظیم‌کاران و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگوسازان فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | چابکی انگشتان | دقت کنترل | چابکی دستی | استدلال قیاسی | درک شفاهی | توجه انتخابی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت انگشتان | دقت کنترل | مهارت دستی | استدلال قیاسی | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، بدنه، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات برقی و الکترونیکی | مونتاژکاران موتورها و ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | ماشین‌کاران و تراشکاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | طراحی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | تجسم فضایی | ثبات دست و بازو | چابکی دستی | هماهنگی اندام‌ها | توجه انتخابی | مرتب‌سازی اطلاعات | حساسیت به مسئله | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | دید دور | انعطاف‌پذیری بدنی | قدرت عضلانی تنه | زمان واکنش | کنترل سرعت | چابکی انگشتان | وضوح گفتار</t>
+          <t>بینایی نزدیک | دقت کنترل | تجسم | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | توجه انتخابی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | وضوح گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، بدنه، تجهیزات و سیستم‌های هواپیما | تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات برقی و الکترونیکی | مونتاژکاران موتورها و ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | ماشین‌کاران و تراشکاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAP | Microsoft Excel | Microsoft Word | Microsoft Outlook | Microsoft Office</t>
+          <t>SAP | نرم‌افزار Microsoft Office | Microsoft Word | Microsoft Outlook | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | هماهنگی اندام‌ها | زمان واکنش | دید نزدیک | چابکی دستی | حساسیت به مسئله | قدرت عضلانی تنه | قدرت ایستای بدنی | دقت کنترل | مرتب‌سازی اطلاعات | سرعت ادراک | توجه انتخابی | چابکی انگشتان | استقامت بدنی | وضوح گفتار | تشخیص گفتار | کنترل سرعت | تجسم فضایی | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | دید دور | انعطاف‌پذیری بدنی | جهت‌گیری پاسخ | انعطاف‌پذیری در دسته‌بندی | درک کتبی | درک شفاهی | توجه شنیداری | درک عمق</t>
+          <t>ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | قدرت تنه | قدرت ایستا | دقت کنترل | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | مهارت انگشتان | استقامت | وضوح گفتار | تشخیص گفتار | کنترل نرخ | تجسم | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | بینایی دور | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | انعطاف‌پذیری دسته‌بندی | درک کتبی | درک شفاهی | توجه شنیداری | درک عمق</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای دستگاه‌های اتصال چسبی | اپراتورهای تجهیزات شیمیایی | اپراتورهای تجهیزات شست‌وشو، تمیزکاری و اسیدشویی فلزات | اپراتورهای تجهیزات تبرید و انجماد | تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های ذوب صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | اپراتورهای کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران مواد و پوشش‌های نسوز کوره (به‌جز بناها) | تنظیم‌کاران و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های جداسازی، فیلتراسیون و تقطیر صنعتی | اپراتورهای ماشین‌آلات رنگرزی و سفیدگری منسوجات | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ریاضیات | طراحی | مکانیک | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری | ساختمان و ساخت‌وساز | مدیریت و امور اداری | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>ریاضیات | طراحی | مکانیک | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری | ساختمان و ساخت‌وساز | مدیریت و اداره | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | تجسم فضایی | حساسیت به مسئله | چابکی دستی | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی انگشتان | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | استدلال ریاضی | درک کتبی | درک شفاهی | قدرت عضلانی تنه | هماهنگی اندام‌ها | دقت کنترل | توانایی کار با اعداد | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | بیان شفاهی | توجه شنیداری | دید دور</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | تجسم | حساسیت به مسئله | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | درک کتبی | درک شفاهی | قدرت تنه | هماهنگی چند عضو | دقت کنترل | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | توجه شنیداری | بینایی دور</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، بدنه، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | کابینت‌سازان و نجاران کارگاهی | نجاران | مونتاژکاران تجهیزات برقی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتورها و ماشین‌آلات صنعتی | ماشین‌کاران و تراشکاران صنعتی | نقشه‌کشان مکانیک | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان صنعتی فلز و پلاستیک | مدل‌سازان صنایع چوب | قالب‌ریزان و شکل‌دهندگان غیر از فلز و پلاستیک | الگو سازان قطعات فلزی و پلاستیکی | الگو سازان صنایع چوب | ورق‌کاران و کانال‌سازان فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | الگوسازان فلز و پلاستیک | الگوسازان چوب | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | شیمی | زبان انگلیسی | مکانیک | مهندسی و فناوری | آموزش و تدریس | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | طراحی | ایمنی و امنیت عمومی | ترابری و حمل‌ونقل</t>
+          <t>تولید و فرآوری | ریاضیات | شیمی | زبان انگلیسی | مکانیک | مهندسی و فناوری | آموزش و پرورش | قانون و دولت | خدمات مشتری و شخصی | طراحی | ایمنی و امنیت عمومی | حمل و نقل</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | وضوح گفتار | هماهنگی اندام‌ها | بیان شفاهی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | قدرت عضلانی تنه | قدرت ایستای بدنی | چابکی انگشتان</t>
+          <t>بینایی نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | وضوح گفتار | هماهنگی چند عضو | بیان شفاهی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | قدرت تنه | قدرت ایستا | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای دستگاه‌های اتصال چسبی | اپراتورهای تجهیزات شیمیایی | تنظیم‌کاران و اپراتورهای دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات | قالب‌ریزان و شکل‌دهندگان غیر از فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین قطعات | ریخته‌گران و بارریزهای فلزات مذاب | تنظیم‌کاران و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های جداسازی، فیلتراسیون و تقطیر صنعتی | اپراتورهای ماشین‌آلات رنگرزی و سفیدگری منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | ریخته‌گران و متصدیان بارریزی مذاب فلزات | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت کنترل | دید نزدیک | تجسم فضایی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراک | زمان واکنش | کنترل سرعت | درک کتبی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | قدرت ایستای بدنی | هماهنگی اندام‌ها</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | سرعت ادراکی | زمان عکس‌العمل | کنترل نرخ | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | قدرت ایستا | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کاران و اپراتورهای دستگاه‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات | تعمیرکاران ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کاران و اپراتورهای دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اره‌کشی چوب | تنظیم‌کاران و اپراتورهای دستگاه‌های برش پارچه و پوشاک | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستای بدنی | قدرت عضلانی تنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی کلی حرکات بدن | تعادل کلی بدن | انعطاف‌پذیری بدنی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ماشین‌کاران و تراشکاران صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | قالب‌سازان و ابزارسازان صنعتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و کشش فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | ریخته‌گران و بارریزهای فلزات مذاب | اپراتورهای کوره‌های تصفیه و ذوب فلزات | مدل‌سازان صنعتی فلز و پلاستیک | اپراتورهای ماشین‌ابزار کنترل عددی رایانه‌ای CNC | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌کنندگان کیفی | سازندگان و مونتاژکاران سازه‌های فلزی | سرپرستان رده اول کارگران تولید و عملیات | سایر کارگران تولید و ساخت</t>
+          <t>تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | جوشکاران، برشکاران و لحیم‌کاران صنعتی | قالب‌سازان و ابزارسازان صنعتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | ریخته‌گران و متصدیان بارریزی مذاب فلزات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | مدل‌سازان فلز و پلاستیک | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | سازندگان و مونتاژکاران سازه‌های فلزی | سرپرستان رده اول کارگران تولید و عملیات | سایر کارگران خطوط تولید</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | استدلال استقرایی | تجسم فضایی | تشخیص تفاوت رنگ‌ها | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | استدلال قیاسی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | تجسم | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک کتبی | درک شفاهی | وضوح گفتار | تشخیص گفتار | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای دستگاه‌های اتصال چسبی | تکنسین‌ها و کارشناسان کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | اپراتورهای ماشین‌ابزار کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزار کنترل عددی رایانه‌ای CNC | طراحان نشر رومیزی و صفحه‌آرایان | مونتاژکاران تجهیزات الکترومکانیکی | قلم‌زنان و حکاکان | تنظیم‌کاران و اپراتورهای دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورهای ماشین‌آلات اداری (به‌جز رایانه) | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین قطعات | تنظیم‌کاران و اپراتورهای ماشین‌آلات تولید محصولات کاغذی | الگو سازان قطعات فلزی و پلاستیکی | پرسنل ظهور عکس و اپراتورهای تجهیزات عکاسی | صحافان و کارگران پرداخت و تکمیل چاپ | اپراتورهای ماشین‌آلات چاپ | هنرمندان و پویانماهای جلوه‌های ویژه</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | مونتاژکاران تجهیزات الکترومکانیکی | حکاکان و اسیدکاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | الگوسازان فلز و پلاستیک | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | کارگران صحافی و تکمیل چاپ | اپراتورهای ماشین‌های چاپ | پویانماها و طراحان جلوه‌های ویژه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
